--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N134_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N134_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>104.9995094876838</v>
+        <v>17.06242029174862</v>
       </c>
       <c r="D2" t="n">
-        <v>102.7089885992647</v>
+        <v>16.69021064738051</v>
       </c>
       <c r="E2" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F2" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>101.9079987551624</v>
+        <v>16.56004979771389</v>
       </c>
       <c r="D3" t="n">
-        <v>51.01448178593205</v>
+        <v>8.289853290213959</v>
       </c>
       <c r="E3" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F3" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>75.19684107381491</v>
+        <v>12.21948667449492</v>
       </c>
       <c r="D4" t="n">
-        <v>73.09237466751235</v>
+        <v>11.87751088347076</v>
       </c>
       <c r="E4" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F4" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>75.28216106306139</v>
+        <v>12.23335117274748</v>
       </c>
       <c r="D5" t="n">
-        <v>72.38229624965737</v>
+        <v>11.76212314056932</v>
       </c>
       <c r="E5" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F5" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.22219674442702</v>
+        <v>10.92360697096939</v>
       </c>
       <c r="D6" t="n">
-        <v>64.28328402869857</v>
+        <v>10.44603365466352</v>
       </c>
       <c r="E6" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F6" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.56561694920227</v>
+        <v>9.679412754245369</v>
       </c>
       <c r="D7" t="n">
-        <v>48.77187942084479</v>
+        <v>7.925430405887279</v>
       </c>
       <c r="E7" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F7" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.22184199407595</v>
+        <v>8.811049324037343</v>
       </c>
       <c r="D8" t="n">
-        <v>39.21214311130615</v>
+        <v>6.371973255587251</v>
       </c>
       <c r="E8" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F8" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>57.98503998432296</v>
+        <v>9.422568997452482</v>
       </c>
       <c r="D9" t="n">
-        <v>23.13015452345303</v>
+        <v>3.758650110061118</v>
       </c>
       <c r="E9" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F9" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.01291431880428</v>
+        <v>7.802098576805696</v>
       </c>
       <c r="D10" t="n">
-        <v>44.70482756841661</v>
+        <v>7.2645344798677</v>
       </c>
       <c r="E10" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F10" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>72.87424915436843</v>
+        <v>11.84206548758487</v>
       </c>
       <c r="D11" t="n">
-        <v>12.17156209414746</v>
+        <v>1.977878840298963</v>
       </c>
       <c r="E11" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F11" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.98607643318464</v>
+        <v>7.310237420392504</v>
       </c>
       <c r="D12" t="n">
-        <v>42.27860018283279</v>
+        <v>6.870272529710329</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F12" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>77.63002683142889</v>
+        <v>12.6148793601072</v>
       </c>
       <c r="D13" t="n">
-        <v>75.06877327225692</v>
+        <v>12.19867565674175</v>
       </c>
       <c r="E13" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F13" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>65.25828311521421</v>
+        <v>10.60447100622231</v>
       </c>
       <c r="D14" t="n">
-        <v>62.88048679630781</v>
+        <v>10.21807910440002</v>
       </c>
       <c r="E14" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F14" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.27212706857077</v>
+        <v>6.38172064864275</v>
       </c>
       <c r="D15" t="n">
-        <v>23.05192094008171</v>
+        <v>3.745937152763278</v>
       </c>
       <c r="E15" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F15" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.06093618105087</v>
+        <v>2.772402129420767</v>
       </c>
       <c r="D16" t="n">
-        <v>17.78710629898389</v>
+        <v>2.890404773584882</v>
       </c>
       <c r="E16" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F16" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>79.30695680196877</v>
+        <v>12.88738048031992</v>
       </c>
       <c r="D17" t="n">
-        <v>77.10344546071418</v>
+        <v>12.52930988736606</v>
       </c>
       <c r="E17" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F17" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38.08634307079433</v>
+        <v>6.189030749004078</v>
       </c>
       <c r="D18" t="n">
-        <v>41.20596225771666</v>
+        <v>6.695968866878958</v>
       </c>
       <c r="E18" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F18" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>75.68770212427603</v>
+        <v>12.29925159519486</v>
       </c>
       <c r="D19" t="n">
-        <v>41.54999458703724</v>
+        <v>6.751874120393552</v>
       </c>
       <c r="E19" t="n">
-        <v>21.43789937428138</v>
+        <v>3.483658648320725</v>
       </c>
       <c r="F19" t="n">
-        <v>23.34409577069453</v>
+        <v>3.793415562737861</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
